--- a/artfynd/A 6798-2026 artfynd.xlsx
+++ b/artfynd/A 6798-2026 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>100293229</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618736.0110559878</v>
+        <v>618736</v>
       </c>
       <c r="R2" t="n">
-        <v>6870864.246885926</v>
+        <v>6870865</v>
       </c>
       <c r="S2" t="n">
         <v>56</v>
@@ -799,47 +794,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100293251</v>
+        <v>102284646</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -855,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618783.421865019</v>
+        <v>618828</v>
       </c>
       <c r="R3" t="n">
-        <v>6870830.1107027</v>
+        <v>6870925</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,22 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +920,7 @@
         <v>101667756</v>
       </c>
       <c r="B4" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618788.2587659622</v>
+        <v>618788</v>
       </c>
       <c r="R4" t="n">
-        <v>6870840.169036702</v>
+        <v>6870840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1047,47 +1032,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102284646</v>
+        <v>100293251</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1103,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618828.2018280518</v>
+        <v>618783</v>
       </c>
       <c r="R5" t="n">
-        <v>6870925.387721455</v>
+        <v>6870830</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,22 +1113,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 6798-2026 artfynd.xlsx
+++ b/artfynd/A 6798-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100293229</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284646</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101667756</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,8 +1172,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100293251</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>